--- a/astro-site/public/dl/kit-tareas-chocolateria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/01-apertura-cierre.xlsx
@@ -730,7 +730,7 @@
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+          <t>Versión 2.1 · octubre 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Verificar el etiquetado de cada producto expuesto: denominación, precio (y precio por kilo si se vende al peso) y los alérgenos declarados — leche, frutos secos, soja, gluten, huevo y sésamo— más las trazas</t>
+          <t>Verificar el etiquetado de cada producto expuesto: denominación, precio (y precio por kilo si se vende al peso) y los alérgenos declarados —leche, huevo, cereales con gluten, soja, cacahuetes, frutos de cáscara, sésamo y sulfitos— más las trazas</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">

--- a/astro-site/public/dl/kit-tareas-chocolateria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/01-apertura-cierre.xlsx
@@ -908,7 +908,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Quien tenga vómitos, diarrea, fiebre o lesiones cutáneas infectadas NO manipula producto: comunicarlo al encargado y reasignar tarea</t>
+          <t>Quien tenga vómitos, diarrea, fiebre o lesiones cutáneas infectadas NO manipula producto ni entra en obrador ni mostrador: comunicarlo al encargado</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Montar vitrina: bombones, tabletas, figuras, trufas</t>
+          <t>Montar vitrina: bombones, tabletas, figuras, trufas; los de ganache de nata fresca y las trufas de nata, solo en vitrina refrigerada a 0-4 °C</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Retirar productos de vitrina y guardar en conservación</t>
+          <t>Retirar productos de vitrina y guardar en conservación; la ganache de nata fresca y las trufas de nata, a la cámara de 0-4 °C</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
